--- a/scripts/imports/fuente/FORMULAS DE COTIZACIÓN.xlsx
+++ b/scripts/imports/fuente/FORMULAS DE COTIZACIÓN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSEPI\scripts\imports\fuente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yusel\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41FD6EB-1565-4A4D-91D7-18E2F1817ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4EDE55-3F8C-4FA0-A87C-E0A1793832C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="3" xr2:uid="{B8EF8191-E857-4727-A73F-34F9264FDB1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{B8EF8191-E857-4727-A73F-34F9264FDB1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -551,7 +554,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -596,20 +599,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -619,20 +622,31 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -650,6 +664,7 @@
     </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -658,9 +673,10 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1009,9 +1025,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1049,7 +1065,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1155,7 +1171,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1297,7 +1313,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2429,7 +2445,7 @@
     <col min="3" max="3" width="14.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="42" customWidth="1"/>
     <col min="7" max="7" width="12.140625" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="15.5703125" style="2" customWidth="1"/>
@@ -2440,28 +2456,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="45">
+      <c r="C1" s="50">
         <v>30</v>
       </c>
-      <c r="D1" s="55">
+      <c r="D1" s="62">
         <v>87</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55">
+      <c r="E1" s="63"/>
+      <c r="F1" s="62">
         <v>80</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="55">
+      <c r="G1" s="47"/>
+      <c r="H1" s="62">
         <v>161.85</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="55">
+      <c r="I1" s="47"/>
+      <c r="J1" s="62">
         <v>52.67</v>
       </c>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
     </row>
     <row r="2" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2479,7 +2495,7 @@
       <c r="E2" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="35" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="30" t="s">
@@ -2500,13 +2516,13 @@
       <c r="L2" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
@@ -2515,7 +2531,7 @@
       <c r="B3" s="31">
         <v>5</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="52">
         <f>((100*2)/10)*$C$1</f>
         <v>600</v>
       </c>
@@ -2527,14 +2543,14 @@
         <f>C3+D3</f>
         <v>1035</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="40">
         <v>16</v>
       </c>
       <c r="G3" s="18">
         <f>F3*$F$1</f>
         <v>1280</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="36">
         <f>F3*$H$1</f>
         <v>2589.6</v>
       </c>
@@ -2545,7 +2561,7 @@
         <f>B3*$J$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="37">
         <f>E3+G3+H3+I3+J3</f>
         <v>10167.950000000001</v>
       </c>
@@ -2557,10 +2573,10 @@
         <f>L3*1.03</f>
         <v>14662.183900000002</v>
       </c>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -2569,7 +2585,7 @@
       <c r="B4" s="26">
         <v>5</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="52">
         <f t="shared" ref="C4:C5" si="0">((100*2)/10)*$C$1</f>
         <v>600</v>
       </c>
@@ -2581,12 +2597,12 @@
         <f>C4+D4</f>
         <v>1035</v>
       </c>
-      <c r="F4" s="37"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="18">
         <f t="shared" ref="G4:G52" si="2">F4*$F$1</f>
         <v>0</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="36">
         <f t="shared" ref="H4:H52" si="3">F4*$H$1</f>
         <v>0</v>
       </c>
@@ -2595,7 +2611,7 @@
         <f t="shared" ref="J4:J52" si="4">B4*$J$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="37">
         <f t="shared" ref="K4:K52" si="5">E4+G4+H4+I4+J4</f>
         <v>1298.3499999999999</v>
       </c>
@@ -2607,10 +2623,10 @@
         <f t="shared" ref="M4:M34" si="7">L4*1.03</f>
         <v>1872.2206999999999</v>
       </c>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
@@ -2619,7 +2635,7 @@
       <c r="B5" s="24">
         <v>5</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="52">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
@@ -2631,12 +2647,12 @@
         <f t="shared" ref="E5:E51" si="8">C5+D5</f>
         <v>1035</v>
       </c>
-      <c r="F5" s="37"/>
+      <c r="F5" s="40"/>
       <c r="G5" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2645,7 +2661,7 @@
         <f t="shared" si="4"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="37">
         <f t="shared" si="5"/>
         <v>1298.3499999999999</v>
       </c>
@@ -2657,10 +2673,10 @@
         <f t="shared" si="7"/>
         <v>1872.2206999999999</v>
       </c>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="57"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
@@ -2669,7 +2685,7 @@
       <c r="B6" s="26">
         <v>2</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -2681,12 +2697,12 @@
         <f t="shared" si="8"/>
         <v>234</v>
       </c>
-      <c r="F6" s="37"/>
+      <c r="F6" s="40"/>
       <c r="G6" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2695,7 +2711,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K6" s="35">
+      <c r="K6" s="37">
         <f t="shared" si="5"/>
         <v>339.34000000000003</v>
       </c>
@@ -2707,10 +2723,10 @@
         <f t="shared" si="7"/>
         <v>489.32828000000006</v>
       </c>
-      <c r="O6" s="51"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="51"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="57"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -2719,7 +2735,7 @@
       <c r="B7" s="24">
         <v>3</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="52">
         <f>((45*2)/10)*$C$1</f>
         <v>270</v>
       </c>
@@ -2731,12 +2747,12 @@
         <f t="shared" si="8"/>
         <v>531</v>
       </c>
-      <c r="F7" s="37"/>
+      <c r="F7" s="40"/>
       <c r="G7" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2745,7 +2761,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="37">
         <f t="shared" si="5"/>
         <v>689.01</v>
       </c>
@@ -2757,10 +2773,10 @@
         <f t="shared" si="7"/>
         <v>993.55241999999998</v>
       </c>
-      <c r="O7" s="51"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="51"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="57"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
@@ -2769,7 +2785,7 @@
       <c r="B8" s="26">
         <v>3</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="52">
         <f>((40*2)/10)*$C$1</f>
         <v>240</v>
       </c>
@@ -2781,12 +2797,12 @@
         <f t="shared" si="8"/>
         <v>501</v>
       </c>
-      <c r="F8" s="37"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2795,7 +2811,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="37">
         <f t="shared" si="5"/>
         <v>659.01</v>
       </c>
@@ -2807,10 +2823,10 @@
         <f t="shared" si="7"/>
         <v>950.29241999999999</v>
       </c>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
@@ -2819,7 +2835,7 @@
       <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="52">
         <f>((45*2)/10)*$C$1</f>
         <v>270</v>
       </c>
@@ -2831,12 +2847,12 @@
         <f t="shared" si="8"/>
         <v>531</v>
       </c>
-      <c r="F9" s="37"/>
+      <c r="F9" s="40"/>
       <c r="G9" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2845,7 +2861,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K9" s="35">
+      <c r="K9" s="37">
         <f t="shared" si="5"/>
         <v>689.01</v>
       </c>
@@ -2857,10 +2873,10 @@
         <f t="shared" si="7"/>
         <v>993.55241999999998</v>
       </c>
-      <c r="O9" s="57"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="57"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
     </row>
     <row r="10" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -2869,7 +2885,7 @@
       <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="52">
         <f>((16*2)/10)*$C$1</f>
         <v>96</v>
       </c>
@@ -2881,12 +2897,12 @@
         <f t="shared" si="8"/>
         <v>270</v>
       </c>
-      <c r="F10" s="37"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2895,7 +2911,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K10" s="35">
+      <c r="K10" s="37">
         <f t="shared" si="5"/>
         <v>375.34000000000003</v>
       </c>
@@ -2907,10 +2923,10 @@
         <f t="shared" si="7"/>
         <v>541.24027999999998</v>
       </c>
-      <c r="O10" s="51"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="51"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="57"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -2919,7 +2935,7 @@
       <c r="B11" s="24">
         <v>5</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="52">
         <f>((200*2)/10)*$C$1</f>
         <v>1200</v>
       </c>
@@ -2931,12 +2947,12 @@
         <f t="shared" si="8"/>
         <v>1635</v>
       </c>
-      <c r="F11" s="37"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2945,7 +2961,7 @@
         <f t="shared" si="4"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="37">
         <f t="shared" si="5"/>
         <v>1898.35</v>
       </c>
@@ -2957,10 +2973,10 @@
         <f t="shared" si="7"/>
         <v>2737.4206999999997</v>
       </c>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -2969,7 +2985,7 @@
       <c r="B12" s="26">
         <v>5</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="52">
         <f>((200*2)/10)*$C$1</f>
         <v>1200</v>
       </c>
@@ -2981,12 +2997,12 @@
         <f t="shared" si="8"/>
         <v>1635</v>
       </c>
-      <c r="F12" s="37"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2995,7 +3011,7 @@
         <f t="shared" si="4"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="K12" s="35">
+      <c r="K12" s="37">
         <f t="shared" si="5"/>
         <v>1898.35</v>
       </c>
@@ -3007,10 +3023,10 @@
         <f t="shared" si="7"/>
         <v>2737.4206999999997</v>
       </c>
-      <c r="O12" s="57"/>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="57"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -3019,7 +3035,7 @@
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="52">
         <f>((45*2)/10)*$C$1</f>
         <v>270</v>
       </c>
@@ -3031,12 +3047,12 @@
         <f t="shared" si="8"/>
         <v>531</v>
       </c>
-      <c r="F13" s="37"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3045,7 +3061,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="37">
         <f t="shared" si="5"/>
         <v>689.01</v>
       </c>
@@ -3057,10 +3073,10 @@
         <f t="shared" si="7"/>
         <v>993.55241999999998</v>
       </c>
-      <c r="O13" s="51"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="51"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="57"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
@@ -3069,7 +3085,7 @@
       <c r="B14" s="26">
         <v>3</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="52">
         <f>((11*2)/10)*$C$1</f>
         <v>66</v>
       </c>
@@ -3081,12 +3097,12 @@
         <f t="shared" si="8"/>
         <v>327</v>
       </c>
-      <c r="F14" s="37"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3095,7 +3111,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="37">
         <f t="shared" si="5"/>
         <v>485.01</v>
       </c>
@@ -3107,10 +3123,10 @@
         <f t="shared" si="7"/>
         <v>699.38441999999986</v>
       </c>
-      <c r="O14" s="51"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="51"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="57"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -3119,7 +3135,7 @@
       <c r="B15" s="24">
         <v>5</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="52">
         <f>((200*2)/10)*$C$1</f>
         <v>1200</v>
       </c>
@@ -3131,12 +3147,12 @@
         <f t="shared" si="8"/>
         <v>1635</v>
       </c>
-      <c r="F15" s="37"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3145,7 +3161,7 @@
         <f t="shared" si="4"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="37">
         <f t="shared" si="5"/>
         <v>1898.35</v>
       </c>
@@ -3157,10 +3173,10 @@
         <f t="shared" si="7"/>
         <v>2737.4206999999997</v>
       </c>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
@@ -3169,7 +3185,7 @@
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="52">
         <f>((35*2)/10)*$C$1</f>
         <v>210</v>
       </c>
@@ -3181,12 +3197,12 @@
         <f t="shared" si="8"/>
         <v>471</v>
       </c>
-      <c r="F16" s="37"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3195,7 +3211,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="37">
         <f t="shared" si="5"/>
         <v>629.01</v>
       </c>
@@ -3207,10 +3223,10 @@
         <f t="shared" si="7"/>
         <v>907.03241999999989</v>
       </c>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
@@ -3219,7 +3235,7 @@
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="52">
         <f>((35*2)/10)*$C$1</f>
         <v>210</v>
       </c>
@@ -3231,12 +3247,12 @@
         <f t="shared" si="8"/>
         <v>471</v>
       </c>
-      <c r="F17" s="37"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3245,7 +3261,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="37">
         <f t="shared" si="5"/>
         <v>629.01</v>
       </c>
@@ -3257,10 +3273,10 @@
         <f t="shared" si="7"/>
         <v>907.03241999999989</v>
       </c>
-      <c r="O17" s="51"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="59"/>
-      <c r="R17" s="51"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="57"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
@@ -3269,7 +3285,7 @@
       <c r="B18" s="26">
         <v>3</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="52">
         <f>((37*2)/10)*$C$1</f>
         <v>222</v>
       </c>
@@ -3281,12 +3297,12 @@
         <f t="shared" si="8"/>
         <v>483</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="40"/>
       <c r="G18" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3295,7 +3311,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="37">
         <f t="shared" si="5"/>
         <v>641.01</v>
       </c>
@@ -3307,10 +3323,10 @@
         <f t="shared" si="7"/>
         <v>924.33641999999986</v>
       </c>
-      <c r="O18" s="51"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="51"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="57"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
@@ -3319,7 +3335,7 @@
       <c r="B19" s="24">
         <v>2</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="52">
         <f>((9*2)/10)*$C$1</f>
         <v>54</v>
       </c>
@@ -3331,12 +3347,12 @@
         <f t="shared" si="8"/>
         <v>228</v>
       </c>
-      <c r="F19" s="37"/>
+      <c r="F19" s="40"/>
       <c r="G19" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3345,7 +3361,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="37">
         <f t="shared" si="5"/>
         <v>333.34000000000003</v>
       </c>
@@ -3357,10 +3373,10 @@
         <f t="shared" si="7"/>
         <v>480.67628000000002</v>
       </c>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -3369,7 +3385,7 @@
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="52">
         <f>((6*2)/10)*$C$1</f>
         <v>36</v>
       </c>
@@ -3381,12 +3397,12 @@
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="F20" s="37"/>
+      <c r="F20" s="40"/>
       <c r="G20" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3395,7 +3411,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="37">
         <f t="shared" si="5"/>
         <v>315.34000000000003</v>
       </c>
@@ -3407,10 +3423,10 @@
         <f t="shared" si="7"/>
         <v>454.72028</v>
       </c>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+      <c r="R20" s="64"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
@@ -3419,7 +3435,7 @@
       <c r="B21" s="24">
         <v>2</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="52">
         <f>((36*2)/10)*$C$1</f>
         <v>216</v>
       </c>
@@ -3431,12 +3447,12 @@
         <f t="shared" si="8"/>
         <v>390</v>
       </c>
-      <c r="F21" s="37"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3445,7 +3461,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="37">
         <f t="shared" si="5"/>
         <v>495.34000000000003</v>
       </c>
@@ -3457,10 +3473,10 @@
         <f t="shared" si="7"/>
         <v>714.28028000000006</v>
       </c>
-      <c r="O21" s="51"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="51"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="57"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
@@ -3469,7 +3485,7 @@
       <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="52">
         <f>((70*2)/10)*$C$1</f>
         <v>420</v>
       </c>
@@ -3481,12 +3497,12 @@
         <f t="shared" si="8"/>
         <v>681</v>
       </c>
-      <c r="F22" s="37"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3495,7 +3511,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="37">
         <f t="shared" si="5"/>
         <v>839.01</v>
       </c>
@@ -3507,10 +3523,10 @@
         <f t="shared" si="7"/>
         <v>1209.8524199999999</v>
       </c>
-      <c r="O22" s="51"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="51"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="57"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -3519,7 +3535,7 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="52">
         <f>((27*2)/10)*$C$1</f>
         <v>162</v>
       </c>
@@ -3531,12 +3547,12 @@
         <f t="shared" si="8"/>
         <v>249</v>
       </c>
-      <c r="F23" s="37"/>
+      <c r="F23" s="40"/>
       <c r="G23" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3545,7 +3561,7 @@
         <f t="shared" si="4"/>
         <v>52.67</v>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="37">
         <f t="shared" si="5"/>
         <v>301.67</v>
       </c>
@@ -3565,7 +3581,7 @@
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="52">
         <f>((76*2)/10)*$C$1</f>
         <v>456</v>
       </c>
@@ -3577,12 +3593,12 @@
         <f t="shared" si="8"/>
         <v>717</v>
       </c>
-      <c r="F24" s="37"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3591,7 +3607,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="37">
         <f t="shared" si="5"/>
         <v>875.01</v>
       </c>
@@ -3611,7 +3627,7 @@
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="52">
         <f>((70*2)/10)*$C$1</f>
         <v>420</v>
       </c>
@@ -3623,12 +3639,12 @@
         <f t="shared" si="8"/>
         <v>681</v>
       </c>
-      <c r="F25" s="37"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3637,7 +3653,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="37">
         <f t="shared" si="5"/>
         <v>839.01</v>
       </c>
@@ -3657,7 +3673,7 @@
       <c r="B26" s="26">
         <v>3</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="52">
         <f>((36*2)/10)*$C$1</f>
         <v>216</v>
       </c>
@@ -3669,12 +3685,12 @@
         <f t="shared" si="8"/>
         <v>477</v>
       </c>
-      <c r="F26" s="37"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3683,7 +3699,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K26" s="35">
+      <c r="K26" s="37">
         <f t="shared" si="5"/>
         <v>635.01</v>
       </c>
@@ -3703,7 +3719,7 @@
       <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="52">
         <f>((3*2)/10)*$C$1</f>
         <v>18</v>
       </c>
@@ -3715,12 +3731,12 @@
         <f t="shared" si="8"/>
         <v>192</v>
       </c>
-      <c r="F27" s="37"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3729,7 +3745,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="37">
         <f t="shared" si="5"/>
         <v>297.34000000000003</v>
       </c>
@@ -3749,7 +3765,7 @@
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="52">
         <f>((16*2)/10)*$C$1</f>
         <v>96</v>
       </c>
@@ -3761,12 +3777,12 @@
         <f t="shared" si="8"/>
         <v>357</v>
       </c>
-      <c r="F28" s="37"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3775,7 +3791,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="37">
         <f t="shared" si="5"/>
         <v>515.01</v>
       </c>
@@ -3795,7 +3811,7 @@
       <c r="B29" s="24">
         <v>2</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="52">
         <f>((32*2)/10)*$C$1</f>
         <v>192</v>
       </c>
@@ -3807,12 +3823,12 @@
         <f t="shared" si="8"/>
         <v>366</v>
       </c>
-      <c r="F29" s="37"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3821,7 +3837,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="37">
         <f t="shared" si="5"/>
         <v>471.34000000000003</v>
       </c>
@@ -3841,7 +3857,7 @@
       <c r="B30" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -3853,12 +3869,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F30" s="37"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3867,7 +3883,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -3887,7 +3903,7 @@
       <c r="B31" s="24">
         <v>5</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="52">
         <f>((200*2)/10)*$C$1</f>
         <v>1200</v>
       </c>
@@ -3899,12 +3915,12 @@
         <f t="shared" si="8"/>
         <v>1635</v>
       </c>
-      <c r="F31" s="37"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3913,7 +3929,7 @@
         <f t="shared" si="4"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="37">
         <f t="shared" si="5"/>
         <v>1898.35</v>
       </c>
@@ -3933,7 +3949,7 @@
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="52">
         <f>((13*2)/10)*$C$1</f>
         <v>78</v>
       </c>
@@ -3945,12 +3961,12 @@
         <f t="shared" si="8"/>
         <v>252</v>
       </c>
-      <c r="F32" s="37"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3959,7 +3975,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="37">
         <f t="shared" si="5"/>
         <v>357.34000000000003</v>
       </c>
@@ -3979,7 +3995,7 @@
       <c r="B33" s="24">
         <v>2</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="52">
         <f>((15*2)/10)*$C$1</f>
         <v>90</v>
       </c>
@@ -3996,7 +4012,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4005,7 +4021,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="37">
         <f t="shared" si="5"/>
         <v>369.34000000000003</v>
       </c>
@@ -4019,13 +4035,13 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="39" t="s">
         <v>51</v>
       </c>
       <c r="B34" s="26">
         <v>4</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="52">
         <f>((80*2)/10)*$C$1</f>
         <v>480</v>
       </c>
@@ -4037,12 +4053,12 @@
         <f>C34+D34</f>
         <v>828</v>
       </c>
-      <c r="F34" s="6"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4051,7 +4067,7 @@
         <f t="shared" si="4"/>
         <v>210.68</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="37">
         <f t="shared" si="5"/>
         <v>1038.68</v>
       </c>
@@ -4065,13 +4081,13 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="40">
         <v>4</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="52">
         <f>((80*2)/10)*$C$1</f>
         <v>480</v>
       </c>
@@ -4083,12 +4099,12 @@
         <f t="shared" si="8"/>
         <v>828</v>
       </c>
-      <c r="F35" s="6"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4097,7 +4113,7 @@
         <f t="shared" si="4"/>
         <v>210.68</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="37">
         <f t="shared" si="5"/>
         <v>1038.68</v>
       </c>
@@ -4111,13 +4127,13 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="39" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="24">
         <v>3</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="52">
         <f>((9*2)/10)*$C$1</f>
         <v>54</v>
       </c>
@@ -4129,12 +4145,12 @@
         <f t="shared" si="8"/>
         <v>315</v>
       </c>
-      <c r="F36" s="6"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4143,7 +4159,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="37">
         <f t="shared" si="5"/>
         <v>473.01</v>
       </c>
@@ -4157,13 +4173,13 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="24">
         <v>3</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="52">
         <f>((20*2)/10)*$C$1</f>
         <v>120</v>
       </c>
@@ -4175,12 +4191,12 @@
         <f t="shared" si="8"/>
         <v>381</v>
       </c>
-      <c r="F37" s="6"/>
+      <c r="F37" s="41"/>
       <c r="G37" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4189,7 +4205,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K37" s="35">
+      <c r="K37" s="37">
         <f t="shared" si="5"/>
         <v>539.01</v>
       </c>
@@ -4203,13 +4219,13 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="39" t="s">
         <v>55</v>
       </c>
       <c r="B38" s="24">
         <v>2</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="52">
         <f>((6*2)/10)*$C$1</f>
         <v>36</v>
       </c>
@@ -4221,12 +4237,12 @@
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="F38" s="6"/>
+      <c r="F38" s="41"/>
       <c r="G38" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4235,7 +4251,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K38" s="35">
+      <c r="K38" s="37">
         <f t="shared" si="5"/>
         <v>315.34000000000003</v>
       </c>
@@ -4249,13 +4265,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="24">
         <v>2</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -4267,12 +4283,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F39" s="6"/>
+      <c r="F39" s="41"/>
       <c r="G39" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4281,7 +4297,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -4295,13 +4311,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="39" t="s">
         <v>58</v>
       </c>
       <c r="B40" s="24">
         <v>2</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -4313,12 +4329,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F40" s="6"/>
+      <c r="F40" s="41"/>
       <c r="G40" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4327,7 +4343,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K40" s="35">
+      <c r="K40" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -4341,13 +4357,13 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="24">
         <v>2</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="52">
         <f>((40*2)/10)*$C$1</f>
         <v>240</v>
       </c>
@@ -4359,12 +4375,12 @@
         <f t="shared" si="8"/>
         <v>414</v>
       </c>
-      <c r="F41" s="6"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4373,7 +4389,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="37">
         <f t="shared" si="5"/>
         <v>519.34</v>
       </c>
@@ -4387,13 +4403,13 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="39" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="26">
         <v>3</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="52">
         <f>((7*2)/10)*$C$1</f>
         <v>42</v>
       </c>
@@ -4405,12 +4421,12 @@
         <f t="shared" si="8"/>
         <v>303</v>
       </c>
-      <c r="F42" s="6"/>
+      <c r="F42" s="41"/>
       <c r="G42" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4419,7 +4435,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K42" s="35">
+      <c r="K42" s="37">
         <f t="shared" si="5"/>
         <v>461.01</v>
       </c>
@@ -4433,13 +4449,13 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="39" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="24">
         <v>2</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -4451,12 +4467,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F43" s="6"/>
+      <c r="F43" s="41"/>
       <c r="G43" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4465,7 +4481,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K43" s="35">
+      <c r="K43" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -4479,13 +4495,13 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="39" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="24">
         <v>2</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="52">
         <f>((10*2)/10)*$C$1</f>
         <v>60</v>
       </c>
@@ -4497,12 +4513,12 @@
         <f t="shared" si="8"/>
         <v>234</v>
       </c>
-      <c r="F44" s="6"/>
+      <c r="F44" s="41"/>
       <c r="G44" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4511,7 +4527,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="37">
         <f t="shared" si="5"/>
         <v>339.34000000000003</v>
       </c>
@@ -4525,13 +4541,13 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="39" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="24">
         <v>2</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="52">
         <f>((6*2)/10)*$C$1</f>
         <v>36</v>
       </c>
@@ -4543,12 +4559,12 @@
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="F45" s="6"/>
+      <c r="F45" s="41"/>
       <c r="G45" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4557,7 +4573,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K45" s="35">
+      <c r="K45" s="37">
         <f t="shared" si="5"/>
         <v>315.34000000000003</v>
       </c>
@@ -4571,13 +4587,13 @@
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="39" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="24">
         <v>2</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -4589,12 +4605,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F46" s="6"/>
+      <c r="F46" s="41"/>
       <c r="G46" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4603,7 +4619,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K46" s="35">
+      <c r="K46" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -4617,13 +4633,13 @@
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="39" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="24">
         <v>2</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="52">
         <f>((20*2)/10)*$C$1</f>
         <v>120</v>
       </c>
@@ -4635,12 +4651,12 @@
         <f t="shared" si="8"/>
         <v>294</v>
       </c>
-      <c r="F47" s="6"/>
+      <c r="F47" s="41"/>
       <c r="G47" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4649,7 +4665,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K47" s="35">
+      <c r="K47" s="37">
         <f t="shared" si="5"/>
         <v>399.34000000000003</v>
       </c>
@@ -4663,13 +4679,13 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="39" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="24">
         <v>2</v>
       </c>
-      <c r="C48" s="47">
+      <c r="C48" s="52">
         <f>((36*2)/10)*$C$1</f>
         <v>216</v>
       </c>
@@ -4681,12 +4697,12 @@
         <f t="shared" si="8"/>
         <v>390</v>
       </c>
-      <c r="F48" s="6"/>
+      <c r="F48" s="41"/>
       <c r="G48" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4695,7 +4711,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K48" s="35">
+      <c r="K48" s="37">
         <f t="shared" si="5"/>
         <v>495.34000000000003</v>
       </c>
@@ -4709,13 +4725,13 @@
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="39" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="26">
         <v>3</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="52">
         <f>((25*2)/10)*$C$1</f>
         <v>150</v>
       </c>
@@ -4727,12 +4743,12 @@
         <f t="shared" si="8"/>
         <v>411</v>
       </c>
-      <c r="F49" s="6"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4741,7 +4757,7 @@
         <f t="shared" si="4"/>
         <v>158.01</v>
       </c>
-      <c r="K49" s="35">
+      <c r="K49" s="37">
         <f t="shared" si="5"/>
         <v>569.01</v>
       </c>
@@ -4755,13 +4771,13 @@
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="39" t="s">
         <v>69</v>
       </c>
       <c r="B50" s="26">
         <v>2</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="52">
         <f>((10*2)/10)*$C$1</f>
         <v>60</v>
       </c>
@@ -4773,12 +4789,12 @@
         <f t="shared" si="8"/>
         <v>234</v>
       </c>
-      <c r="F50" s="6"/>
+      <c r="F50" s="41"/>
       <c r="G50" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H50" s="18">
+      <c r="H50" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4787,7 +4803,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K50" s="35">
+      <c r="K50" s="37">
         <f t="shared" si="5"/>
         <v>339.34000000000003</v>
       </c>
@@ -4801,13 +4817,13 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="39" t="s">
         <v>70</v>
       </c>
       <c r="B51" s="24">
         <v>2</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -4819,12 +4835,12 @@
         <f t="shared" si="8"/>
         <v>222</v>
       </c>
-      <c r="F51" s="6"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H51" s="18">
+      <c r="H51" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4833,7 +4849,7 @@
         <f t="shared" si="4"/>
         <v>105.34</v>
       </c>
-      <c r="K51" s="35">
+      <c r="K51" s="37">
         <f t="shared" si="5"/>
         <v>327.34000000000003</v>
       </c>
@@ -4847,13 +4863,13 @@
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="39" t="s">
         <v>85</v>
       </c>
       <c r="B52" s="24">
         <v>4</v>
       </c>
-      <c r="C52" s="47">
+      <c r="C52" s="52">
         <f>((80*2)/10)*$C$1</f>
         <v>480</v>
       </c>
@@ -4865,12 +4881,12 @@
         <f t="shared" ref="E52" si="11">B52*$D$1</f>
         <v>348</v>
       </c>
-      <c r="F52" s="6"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H52" s="18">
+      <c r="H52" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4879,7 +4895,7 @@
         <f t="shared" si="4"/>
         <v>210.68</v>
       </c>
-      <c r="K52" s="35">
+      <c r="K52" s="37">
         <f t="shared" si="5"/>
         <v>558.68000000000006</v>
       </c>
@@ -4893,15 +4909,15 @@
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C53" s="35"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="53"/>
-      <c r="K53" s="51"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="60"/>
+      <c r="J53" s="60"/>
+      <c r="K53" s="57"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I61" s="2" t="s">
@@ -4942,15 +4958,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C1" s="46">
+      <c r="C1" s="51">
         <v>30</v>
       </c>
-      <c r="D1" s="54">
+      <c r="D1" s="61">
         <v>87</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="55">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="62">
         <v>52.67</v>
       </c>
     </row>
@@ -4982,7 +4998,7 @@
       <c r="I2" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="38" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4993,7 +5009,7 @@
       <c r="B3" s="31">
         <v>5</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -5010,7 +5026,7 @@
         <f>B3*$G$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="37">
         <f>E3+F3+G3</f>
         <v>1298.3499999999999</v>
       </c>
@@ -5030,7 +5046,7 @@
       <c r="B4" s="26">
         <v>5</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -5047,7 +5063,7 @@
         <f t="shared" ref="G4:G51" si="2">B4*$G$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="37">
         <f t="shared" ref="H4:H52" si="3">E4+F4+G4</f>
         <v>1298.3499999999999</v>
       </c>
@@ -5067,7 +5083,7 @@
       <c r="B5" s="24">
         <v>5</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -5084,7 +5100,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="37">
         <f t="shared" si="3"/>
         <v>1298.3499999999999</v>
       </c>
@@ -5104,7 +5120,7 @@
       <c r="B6" s="26">
         <v>2</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -5121,7 +5137,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -5141,7 +5157,7 @@
       <c r="B7" s="24">
         <v>3</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -5158,7 +5174,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -5178,7 +5194,7 @@
       <c r="B8" s="26">
         <v>3</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="52">
         <f>((40*2)/10)*C1</f>
         <v>240</v>
       </c>
@@ -5195,7 +5211,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="37">
         <f t="shared" si="3"/>
         <v>659.01</v>
       </c>
@@ -5215,7 +5231,7 @@
       <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -5232,7 +5248,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -5252,7 +5268,7 @@
       <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="52">
         <f>((16*2)/10)*C8</f>
         <v>768</v>
       </c>
@@ -5269,7 +5285,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="37">
         <f t="shared" si="3"/>
         <v>1047.3399999999999</v>
       </c>
@@ -5289,7 +5305,7 @@
       <c r="B11" s="24">
         <v>5</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -5306,7 +5322,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -5326,7 +5342,7 @@
       <c r="B12" s="26">
         <v>5</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -5343,7 +5359,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -5363,7 +5379,7 @@
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -5380,7 +5396,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -5400,7 +5416,7 @@
       <c r="B14" s="26">
         <v>3</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="52">
         <f>((11*2)/10)*C1</f>
         <v>66</v>
       </c>
@@ -5417,7 +5433,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="37">
         <f t="shared" si="3"/>
         <v>485.01</v>
       </c>
@@ -5437,7 +5453,7 @@
       <c r="B15" s="24">
         <v>5</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -5454,7 +5470,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -5474,7 +5490,7 @@
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="52">
         <f>((35*2)/10)*C1</f>
         <v>210</v>
       </c>
@@ -5491,7 +5507,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="37">
         <f t="shared" si="3"/>
         <v>629.01</v>
       </c>
@@ -5511,7 +5527,7 @@
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="52">
         <f>((35*2)/10)*C1</f>
         <v>210</v>
       </c>
@@ -5528,7 +5544,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>629.01</v>
       </c>
@@ -5548,7 +5564,7 @@
       <c r="B18" s="26">
         <v>3</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="52">
         <f>((37*2)/10)*C1</f>
         <v>222</v>
       </c>
@@ -5565,7 +5581,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="37">
         <f t="shared" si="3"/>
         <v>641.01</v>
       </c>
@@ -5585,7 +5601,7 @@
       <c r="B19" s="24">
         <v>2</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="52">
         <f>((9*2)/10)*C1</f>
         <v>54</v>
       </c>
@@ -5602,7 +5618,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="37">
         <f t="shared" si="3"/>
         <v>333.34000000000003</v>
       </c>
@@ -5622,7 +5638,7 @@
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -5639,7 +5655,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -5659,7 +5675,7 @@
       <c r="B21" s="24">
         <v>2</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -5676,7 +5692,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -5696,7 +5712,7 @@
       <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -5713,7 +5729,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -5733,7 +5749,7 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="52">
         <f>((27*2)/10)*C1</f>
         <v>162</v>
       </c>
@@ -5750,7 +5766,7 @@
         <f t="shared" si="2"/>
         <v>52.67</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="37">
         <f t="shared" si="3"/>
         <v>301.67</v>
       </c>
@@ -5770,7 +5786,7 @@
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="52">
         <f>((76*2)/10)*C1</f>
         <v>456</v>
       </c>
@@ -5787,7 +5803,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="37">
         <f t="shared" si="3"/>
         <v>875.01</v>
       </c>
@@ -5807,7 +5823,7 @@
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -5824,7 +5840,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -5844,7 +5860,7 @@
       <c r="B26" s="26">
         <v>3</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -5861,7 +5877,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -5881,7 +5897,7 @@
       <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -5898,7 +5914,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -5918,7 +5934,7 @@
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="52">
         <f>((16*2)/10)*C1</f>
         <v>96</v>
       </c>
@@ -5935,7 +5951,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="37">
         <f t="shared" si="3"/>
         <v>515.01</v>
       </c>
@@ -5955,7 +5971,7 @@
       <c r="B29" s="24">
         <v>2</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="52">
         <f>((32*2)/10)*C1</f>
         <v>192</v>
       </c>
@@ -5972,7 +5988,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="37">
         <f t="shared" si="3"/>
         <v>471.34000000000003</v>
       </c>
@@ -5992,7 +6008,7 @@
       <c r="B30" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -6009,7 +6025,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -6029,7 +6045,7 @@
       <c r="B31" s="24">
         <v>5</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -6046,7 +6062,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -6066,7 +6082,7 @@
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="52">
         <f>((13*2)/10)*C1</f>
         <v>78</v>
       </c>
@@ -6083,7 +6099,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="37">
         <f t="shared" si="3"/>
         <v>357.34000000000003</v>
       </c>
@@ -6103,7 +6119,7 @@
       <c r="B33" s="24">
         <v>2</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="52">
         <f>((15*2)/10)*C1</f>
         <v>90</v>
       </c>
@@ -6120,7 +6136,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="37">
         <f t="shared" si="3"/>
         <v>369.34000000000003</v>
       </c>
@@ -6134,13 +6150,13 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="39" t="s">
         <v>51</v>
       </c>
       <c r="B34" s="26">
         <v>4</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="52">
         <f>((110*2)/10)*C1</f>
         <v>660</v>
       </c>
@@ -6157,7 +6173,7 @@
         <f t="shared" si="2"/>
         <v>210.68</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="37">
         <f t="shared" si="3"/>
         <v>1218.68</v>
       </c>
@@ -6171,13 +6187,13 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="40">
         <v>4</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="52">
         <f>((80*2)/10)*C1</f>
         <v>480</v>
       </c>
@@ -6194,7 +6210,7 @@
         <f t="shared" si="2"/>
         <v>210.68</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="37">
         <f t="shared" si="3"/>
         <v>1038.68</v>
       </c>
@@ -6208,13 +6224,13 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="39" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="24">
         <v>3</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="52">
         <f>((9*2)/10)*C1</f>
         <v>54</v>
       </c>
@@ -6231,7 +6247,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="37">
         <f t="shared" si="3"/>
         <v>473.01</v>
       </c>
@@ -6245,13 +6261,13 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="24">
         <v>3</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="52">
         <f>((20*2)/10)*C1</f>
         <v>120</v>
       </c>
@@ -6268,7 +6284,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H37" s="35">
+      <c r="H37" s="37">
         <f t="shared" si="3"/>
         <v>539.01</v>
       </c>
@@ -6282,13 +6298,13 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="39" t="s">
         <v>55</v>
       </c>
       <c r="B38" s="24">
         <v>2</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -6305,7 +6321,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -6319,13 +6335,13 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="24">
         <v>2</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -6342,7 +6358,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -6356,13 +6372,13 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="39" t="s">
         <v>58</v>
       </c>
       <c r="B40" s="24">
         <v>2</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -6379,7 +6395,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H40" s="35">
+      <c r="H40" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -6393,13 +6409,13 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="24">
         <v>2</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="52">
         <f>((40*2)/10)*C1</f>
         <v>240</v>
       </c>
@@ -6416,7 +6432,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="37">
         <f t="shared" si="3"/>
         <v>519.34</v>
       </c>
@@ -6430,13 +6446,13 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="39" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="26">
         <v>3</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="52">
         <f>((7*2)/10)*C1</f>
         <v>42</v>
       </c>
@@ -6453,7 +6469,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="37">
         <f t="shared" si="3"/>
         <v>461.01</v>
       </c>
@@ -6467,13 +6483,13 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="39" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="24">
         <v>2</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -6490,7 +6506,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H43" s="35">
+      <c r="H43" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -6504,13 +6520,13 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="39" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="24">
         <v>2</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -6527,7 +6543,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -6541,13 +6557,13 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="39" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="24">
         <v>2</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -6564,7 +6580,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -6578,13 +6594,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="39" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="24">
         <v>2</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -6601,7 +6617,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -6615,13 +6631,13 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="39" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="24">
         <v>2</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="52">
         <f>((20*2)/10)*C1</f>
         <v>120</v>
       </c>
@@ -6638,7 +6654,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="37">
         <f t="shared" si="3"/>
         <v>399.34000000000003</v>
       </c>
@@ -6652,13 +6668,13 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="39" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="24">
         <v>2</v>
       </c>
-      <c r="C48" s="47">
+      <c r="C48" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -6675,7 +6691,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -6689,13 +6705,13 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="39" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="26">
         <v>3</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="52">
         <f>((25*2)/10)*C1</f>
         <v>150</v>
       </c>
@@ -6712,7 +6728,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="37">
         <f t="shared" si="3"/>
         <v>569.01</v>
       </c>
@@ -6726,13 +6742,13 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="39" t="s">
         <v>69</v>
       </c>
       <c r="B50" s="26">
         <v>2</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -6749,7 +6765,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -6763,13 +6779,13 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="39" t="s">
         <v>70</v>
       </c>
       <c r="B51" s="24">
         <v>2</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="52">
         <f>((10*2)/10)*$C$1</f>
         <v>60</v>
       </c>
@@ -6786,7 +6802,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -6800,13 +6816,13 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="39" t="s">
         <v>85</v>
       </c>
       <c r="B52" s="24">
         <v>4</v>
       </c>
-      <c r="C52" s="47">
+      <c r="C52" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -6818,12 +6834,12 @@
         <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="F52" s="21"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="18">
         <f>B52*$G$1</f>
         <v>210.68</v>
       </c>
-      <c r="H52" s="35">
+      <c r="H52" s="37">
         <f t="shared" si="3"/>
         <v>606.68000000000006</v>
       </c>
@@ -6837,8 +6853,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="38"/>
-      <c r="G53" s="53"/>
+      <c r="A53" s="43"/>
+      <c r="G53" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6869,43 +6885,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="43">
+      <c r="B1" s="48">
         <v>650</v>
       </c>
-      <c r="C1" s="43">
+      <c r="C1" s="48">
         <v>700</v>
       </c>
-      <c r="D1" s="43">
+      <c r="D1" s="48">
         <v>450</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="48">
         <v>900</v>
       </c>
-      <c r="F1" s="43">
+      <c r="F1" s="48">
         <v>350</v>
       </c>
-      <c r="G1" s="43">
+      <c r="G1" s="48">
         <v>600</v>
       </c>
-      <c r="H1" s="43">
+      <c r="H1" s="48">
         <v>1100</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="48">
         <v>150</v>
       </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="45">
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="50">
         <v>52.67</v>
       </c>
-      <c r="P1" s="46">
+      <c r="P1" s="51">
         <v>30</v>
       </c>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="55">
+      <c r="Q1" s="51"/>
+      <c r="R1" s="62">
         <v>161.85</v>
       </c>
     </row>
@@ -6973,7 +6989,7 @@
       <c r="U2" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="44" t="s">
         <v>92</v>
       </c>
     </row>
@@ -6981,19 +6997,19 @@
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54">
         <f>SUM(B3:I3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="47">
+      <c r="K3" s="52">
         <f>SUM($D$1*D3)+($E$1*E3)+($F$1*F3)+($B$1*B3)+($C$1*C3)+($G$1*G3)+($H$1*H3)+($I$1*I3)</f>
         <v>0</v>
       </c>
@@ -7003,53 +7019,53 @@
         <v>0</v>
       </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="47">
+      <c r="O3" s="52">
         <f>J3*$O$1</f>
         <v>0</v>
       </c>
-      <c r="P3" s="47">
+      <c r="P3" s="52">
         <f>((100*2)/10)*P1</f>
         <v>600</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="47">
+      <c r="Q3" s="41"/>
+      <c r="R3" s="52">
         <f>Q3*$R$1</f>
         <v>0</v>
       </c>
-      <c r="S3" s="47">
+      <c r="S3" s="52">
         <f>K3+M3+LN3+SN3+O3+N3+P3+R3</f>
         <v>600</v>
       </c>
-      <c r="T3" s="35">
-        <f>S3*0.03</f>
-        <v>18</v>
-      </c>
-      <c r="U3" s="47">
+      <c r="T3" s="37">
+        <f>S3*0.3</f>
+        <v>180</v>
+      </c>
+      <c r="U3" s="52">
         <f>S3+T3</f>
-        <v>618</v>
-      </c>
-      <c r="V3" s="40">
+        <v>780</v>
+      </c>
+      <c r="V3" s="45">
         <f>U3*0.05</f>
-        <v>30.900000000000002</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48">
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54">
         <f t="shared" ref="J4:J52" si="0">SUM(B4:I4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="52">
         <f t="shared" ref="K4:K52" si="1">SUM($D$1*D4)+($E$1*E4)+($F$1*F4)+($B$1*B4)+($C$1*C4)+($G$1*G4)+($H$1*H4)+($I$1*I4)</f>
         <v>0</v>
       </c>
@@ -7059,49 +7075,49 @@
         <v>0</v>
       </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="47">
+      <c r="O4" s="52">
         <f t="shared" ref="O4:O52" si="3">J4*$O$1</f>
         <v>0</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="52">
         <f>((100*2)/10)*P1</f>
         <v>600</v>
       </c>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47">
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52">
         <f t="shared" ref="R4:R52" si="4">Q4*$R$1</f>
         <v>0</v>
       </c>
-      <c r="S4" s="47">
+      <c r="S4" s="52">
         <f t="shared" ref="S4:S52" si="5">K4+M4+L4+N4+SN4+O4+P4+R4</f>
         <v>600</v>
       </c>
-      <c r="T4" s="35">
-        <f t="shared" ref="T4:T52" si="6">S4*0.03</f>
-        <v>18</v>
-      </c>
-      <c r="U4" s="47">
-        <f>S4+T4</f>
-        <v>618</v>
+      <c r="T4" s="37">
+        <f t="shared" ref="T4:T52" si="6">S4*0.3</f>
+        <v>180</v>
+      </c>
+      <c r="U4" s="52">
+        <f t="shared" ref="U4:U52" si="7">S4+T4</f>
+        <v>780</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="47">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7111,49 +7127,49 @@
         <v>0</v>
       </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P5" s="47">
+      <c r="O5" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="52">
         <f>((100*2)/10)*P1</f>
         <v>600</v>
       </c>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="47">
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="52">
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="T5" s="35">
+      <c r="T5" s="37">
         <f t="shared" si="6"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="47">
-        <f t="shared" ref="U4:U52" si="7">S5+T5</f>
-        <v>618</v>
+        <v>180</v>
+      </c>
+      <c r="U5" s="52">
+        <f t="shared" si="7"/>
+        <v>780</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="47">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7163,49 +7179,49 @@
         <v>0</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="47">
+      <c r="O6" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="52">
         <f>((10*2)/10)*P1</f>
         <v>60</v>
       </c>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="47">
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="52">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="T6" s="35">
+      <c r="T6" s="37">
         <f t="shared" si="6"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="U6" s="47">
+        <v>18</v>
+      </c>
+      <c r="U6" s="52">
         <f t="shared" si="7"/>
-        <v>61.8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="47">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7215,49 +7231,49 @@
         <v>0</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P7" s="47">
+      <c r="O7" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="52">
         <f>((45*2)/10)*P1</f>
         <v>270</v>
       </c>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S7" s="47">
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="52">
         <f t="shared" si="5"/>
         <v>270</v>
       </c>
-      <c r="T7" s="35">
+      <c r="T7" s="37">
         <f t="shared" si="6"/>
-        <v>8.1</v>
-      </c>
-      <c r="U7" s="47">
+        <v>81</v>
+      </c>
+      <c r="U7" s="52">
         <f t="shared" si="7"/>
-        <v>278.10000000000002</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="47">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7267,49 +7283,49 @@
         <v>0</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="47">
+      <c r="O8" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="52">
         <f>((40*2)/10)*P1</f>
         <v>240</v>
       </c>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="47">
+      <c r="Q8" s="52"/>
+      <c r="R8" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="52">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="T8" s="35">
+      <c r="T8" s="37">
         <f t="shared" si="6"/>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="U8" s="47">
+        <v>72</v>
+      </c>
+      <c r="U8" s="52">
         <f t="shared" si="7"/>
-        <v>247.2</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="47">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7319,49 +7335,49 @@
         <v>0</v>
       </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P9" s="47">
+      <c r="O9" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="52">
         <f>((45*2)/10)*P1</f>
         <v>270</v>
       </c>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="47">
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="52">
         <f t="shared" si="5"/>
         <v>270</v>
       </c>
-      <c r="T9" s="35">
+      <c r="T9" s="37">
         <f t="shared" si="6"/>
-        <v>8.1</v>
-      </c>
-      <c r="U9" s="47">
+        <v>81</v>
+      </c>
+      <c r="U9" s="52">
         <f t="shared" si="7"/>
-        <v>278.10000000000002</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="47">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7371,49 +7387,49 @@
         <v>0</v>
       </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="47">
+      <c r="O10" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="52">
         <f>((16*2)/10)*P8</f>
         <v>768</v>
       </c>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="47">
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="52">
         <f t="shared" si="5"/>
         <v>768</v>
       </c>
-      <c r="T10" s="35">
+      <c r="T10" s="37">
         <f t="shared" si="6"/>
-        <v>23.04</v>
-      </c>
-      <c r="U10" s="47">
+        <v>230.39999999999998</v>
+      </c>
+      <c r="U10" s="52">
         <f t="shared" si="7"/>
-        <v>791.04</v>
+        <v>998.4</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="47">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7423,49 +7439,49 @@
         <v>0</v>
       </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="47">
+      <c r="O11" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="52">
         <f>((200*2)/10)*P1</f>
         <v>1200</v>
       </c>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="47">
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="52">
         <f t="shared" si="5"/>
         <v>1200</v>
       </c>
-      <c r="T11" s="35">
+      <c r="T11" s="37">
         <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-      <c r="U11" s="47">
+        <v>360</v>
+      </c>
+      <c r="U11" s="52">
         <f t="shared" si="7"/>
-        <v>1236</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="47">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7475,49 +7491,49 @@
         <v>0</v>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="47">
+      <c r="O12" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="52">
         <f>((200*2)/10)*P1</f>
         <v>1200</v>
       </c>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="47">
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="52">
         <f t="shared" si="5"/>
         <v>1200</v>
       </c>
-      <c r="T12" s="35">
+      <c r="T12" s="37">
         <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-      <c r="U12" s="47">
+        <v>360</v>
+      </c>
+      <c r="U12" s="52">
         <f t="shared" si="7"/>
-        <v>1236</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="47">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7527,49 +7543,49 @@
         <v>0</v>
       </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="47">
+      <c r="O13" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="52">
         <f>((45*2)/10)*P1</f>
         <v>270</v>
       </c>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="47">
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="52">
         <f t="shared" si="5"/>
         <v>270</v>
       </c>
-      <c r="T13" s="35">
+      <c r="T13" s="37">
         <f t="shared" si="6"/>
-        <v>8.1</v>
-      </c>
-      <c r="U13" s="47">
+        <v>81</v>
+      </c>
+      <c r="U13" s="52">
         <f t="shared" si="7"/>
-        <v>278.10000000000002</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="47">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7579,49 +7595,49 @@
         <v>0</v>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="47">
+      <c r="O14" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="52">
         <f>((11*2)/10)*P1</f>
         <v>66</v>
       </c>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="47">
+      <c r="Q14" s="52"/>
+      <c r="R14" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="52">
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
-      <c r="T14" s="35">
+      <c r="T14" s="37">
         <f t="shared" si="6"/>
-        <v>1.98</v>
-      </c>
-      <c r="U14" s="47">
+        <v>19.8</v>
+      </c>
+      <c r="U14" s="52">
         <f t="shared" si="7"/>
-        <v>67.98</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="47">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7631,49 +7647,49 @@
         <v>0</v>
       </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="47">
+      <c r="O15" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="52">
         <f>((200*2)/10)*P1</f>
         <v>1200</v>
       </c>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="47">
+      <c r="Q15" s="52"/>
+      <c r="R15" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="52">
         <f t="shared" si="5"/>
         <v>1200</v>
       </c>
-      <c r="T15" s="35">
+      <c r="T15" s="37">
         <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-      <c r="U15" s="47">
+        <v>360</v>
+      </c>
+      <c r="U15" s="52">
         <f t="shared" si="7"/>
-        <v>1236</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="47">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7683,49 +7699,49 @@
         <v>0</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="47">
+      <c r="O16" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="52">
         <f>((35*2)/10)*P1</f>
         <v>210</v>
       </c>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="47">
+      <c r="Q16" s="52"/>
+      <c r="R16" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="52">
         <f t="shared" si="5"/>
         <v>210</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="37">
         <f t="shared" si="6"/>
-        <v>6.3</v>
-      </c>
-      <c r="U16" s="47">
+        <v>63</v>
+      </c>
+      <c r="U16" s="52">
         <f t="shared" si="7"/>
-        <v>216.3</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="47">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7735,49 +7751,49 @@
         <v>0</v>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="47">
+      <c r="O17" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="52">
         <f>((35*2)/10)*P1</f>
         <v>210</v>
       </c>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="47">
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="52">
         <f t="shared" si="5"/>
         <v>210</v>
       </c>
-      <c r="T17" s="35">
+      <c r="T17" s="37">
         <f t="shared" si="6"/>
-        <v>6.3</v>
-      </c>
-      <c r="U17" s="47">
+        <v>63</v>
+      </c>
+      <c r="U17" s="52">
         <f t="shared" si="7"/>
-        <v>216.3</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="47">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7787,49 +7803,49 @@
         <v>0</v>
       </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="47">
+      <c r="O18" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="52">
         <f>((37*2)/10)*P1</f>
         <v>222</v>
       </c>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="47">
+      <c r="Q18" s="52"/>
+      <c r="R18" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="52">
         <f t="shared" si="5"/>
         <v>222</v>
       </c>
-      <c r="T18" s="35">
+      <c r="T18" s="37">
         <f t="shared" si="6"/>
-        <v>6.66</v>
-      </c>
-      <c r="U18" s="47">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="U18" s="52">
         <f t="shared" si="7"/>
-        <v>228.66</v>
+        <v>288.60000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="47">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7839,49 +7855,49 @@
         <v>0</v>
       </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="47">
+      <c r="O19" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="52">
         <f>((9*2)/10)*P1</f>
         <v>54</v>
       </c>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="47">
+      <c r="Q19" s="52"/>
+      <c r="R19" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="52">
         <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="T19" s="35">
+      <c r="T19" s="37">
         <f t="shared" si="6"/>
-        <v>1.6199999999999999</v>
-      </c>
-      <c r="U19" s="47">
+        <v>16.2</v>
+      </c>
+      <c r="U19" s="52">
         <f t="shared" si="7"/>
-        <v>55.62</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="47">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7891,49 +7907,49 @@
         <v>0</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="47">
+      <c r="O20" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="52">
         <f>((6*2)/10)*P1</f>
         <v>36</v>
       </c>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="47">
+      <c r="Q20" s="52"/>
+      <c r="R20" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="52">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="T20" s="35">
+      <c r="T20" s="37">
         <f t="shared" si="6"/>
-        <v>1.08</v>
-      </c>
-      <c r="U20" s="47">
+        <v>10.799999999999999</v>
+      </c>
+      <c r="U20" s="52">
         <f t="shared" si="7"/>
-        <v>37.08</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="47">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7943,49 +7959,49 @@
         <v>0</v>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="47">
+      <c r="O21" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="52">
         <f>((36*2)/10)*P1</f>
         <v>216</v>
       </c>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="47">
+      <c r="Q21" s="52"/>
+      <c r="R21" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="52">
         <f t="shared" si="5"/>
         <v>216</v>
       </c>
-      <c r="T21" s="35">
+      <c r="T21" s="37">
         <f t="shared" si="6"/>
-        <v>6.4799999999999995</v>
-      </c>
-      <c r="U21" s="47">
+        <v>64.8</v>
+      </c>
+      <c r="U21" s="52">
         <f t="shared" si="7"/>
-        <v>222.48</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="47">
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7995,49 +8011,49 @@
         <v>0</v>
       </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="47">
+      <c r="O22" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="52">
         <f>((70*2)/10)*P1</f>
         <v>420</v>
       </c>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="47">
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="52">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="37">
         <f t="shared" si="6"/>
-        <v>12.6</v>
-      </c>
-      <c r="U22" s="47">
+        <v>126</v>
+      </c>
+      <c r="U22" s="52">
         <f t="shared" si="7"/>
-        <v>432.6</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="47">
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8047,49 +8063,49 @@
         <v>0</v>
       </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="47">
+      <c r="O23" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="52">
         <f>((27*2)/10)*P1</f>
         <v>162</v>
       </c>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="47">
+      <c r="Q23" s="52"/>
+      <c r="R23" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="52">
         <f t="shared" si="5"/>
         <v>162</v>
       </c>
-      <c r="T23" s="35">
+      <c r="T23" s="37">
         <f t="shared" si="6"/>
-        <v>4.8599999999999994</v>
-      </c>
-      <c r="U23" s="47">
+        <v>48.6</v>
+      </c>
+      <c r="U23" s="52">
         <f t="shared" si="7"/>
-        <v>166.86</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="47">
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8099,49 +8115,49 @@
         <v>0</v>
       </c>
       <c r="N24" s="7"/>
-      <c r="O24" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="47">
+      <c r="O24" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="52">
         <f>((76*2)/10)*P1</f>
         <v>456</v>
       </c>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="47">
+      <c r="Q24" s="52"/>
+      <c r="R24" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="52">
         <f t="shared" si="5"/>
         <v>456</v>
       </c>
-      <c r="T24" s="35">
+      <c r="T24" s="37">
         <f t="shared" si="6"/>
-        <v>13.68</v>
-      </c>
-      <c r="U24" s="47">
+        <v>136.79999999999998</v>
+      </c>
+      <c r="U24" s="52">
         <f t="shared" si="7"/>
-        <v>469.68</v>
+        <v>592.79999999999995</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="47">
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8151,49 +8167,49 @@
         <v>0</v>
       </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="47">
+      <c r="O25" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="52">
         <f>((70*2)/10)*P1</f>
         <v>420</v>
       </c>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="47">
+      <c r="Q25" s="52"/>
+      <c r="R25" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="52">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="T25" s="35">
+      <c r="T25" s="37">
         <f t="shared" si="6"/>
-        <v>12.6</v>
-      </c>
-      <c r="U25" s="47">
+        <v>126</v>
+      </c>
+      <c r="U25" s="52">
         <f t="shared" si="7"/>
-        <v>432.6</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="47">
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8203,49 +8219,49 @@
         <v>0</v>
       </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="47">
+      <c r="O26" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="52">
         <f>((36*2)/10)*P1</f>
         <v>216</v>
       </c>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="47">
+      <c r="Q26" s="52"/>
+      <c r="R26" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="52">
         <f t="shared" si="5"/>
         <v>216</v>
       </c>
-      <c r="T26" s="35">
+      <c r="T26" s="37">
         <f t="shared" si="6"/>
-        <v>6.4799999999999995</v>
-      </c>
-      <c r="U26" s="47">
+        <v>64.8</v>
+      </c>
+      <c r="U26" s="52">
         <f t="shared" si="7"/>
-        <v>222.48</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="47">
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8255,1330 +8271,1330 @@
         <v>0</v>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="47">
+      <c r="O27" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="52">
         <f>((3*2)/10)*P1</f>
         <v>18</v>
       </c>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="47">
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="52">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="37">
         <f t="shared" si="6"/>
-        <v>0.54</v>
-      </c>
-      <c r="U27" s="47">
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="U27" s="52">
         <f t="shared" si="7"/>
-        <v>18.54</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="21"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="53"/>
       <c r="M28" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="47">
+      <c r="O28" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="52">
         <f>((16*2)/10)*P1</f>
         <v>96</v>
       </c>
-      <c r="Q28" s="47"/>
-      <c r="R28" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="47">
+      <c r="Q28" s="52"/>
+      <c r="R28" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="52">
         <f t="shared" si="5"/>
         <v>96</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="37">
         <f t="shared" si="6"/>
-        <v>2.88</v>
-      </c>
-      <c r="U28" s="47">
+        <v>28.799999999999997</v>
+      </c>
+      <c r="U28" s="52">
         <f t="shared" si="7"/>
-        <v>98.88</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="21"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="53"/>
       <c r="M29" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N29" s="7"/>
-      <c r="O29" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="47">
+      <c r="O29" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="52">
         <f>((32*2)/10)*P1</f>
         <v>192</v>
       </c>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="47">
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="52">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
-      <c r="T29" s="35">
+      <c r="T29" s="37">
         <f t="shared" si="6"/>
-        <v>5.76</v>
-      </c>
-      <c r="U29" s="47">
+        <v>57.599999999999994</v>
+      </c>
+      <c r="U29" s="52">
         <f t="shared" si="7"/>
-        <v>197.76</v>
+        <v>249.6</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="21"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="53"/>
       <c r="M30" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N30" s="7"/>
-      <c r="O30" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="47">
+      <c r="O30" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="52">
         <f>((8*2)/10)*P1</f>
         <v>48</v>
       </c>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="47">
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="52">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="37">
         <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U30" s="47">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U30" s="52">
         <f t="shared" si="7"/>
-        <v>49.44</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="21"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="53"/>
       <c r="M31" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N31" s="7"/>
-      <c r="O31" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="47">
+      <c r="O31" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="52">
         <f>((200*2)/10)*P1</f>
         <v>1200</v>
       </c>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="47">
+      <c r="Q31" s="52"/>
+      <c r="R31" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="52">
         <f t="shared" si="5"/>
         <v>1200</v>
       </c>
-      <c r="T31" s="35">
+      <c r="T31" s="37">
         <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-      <c r="U31" s="47">
+        <v>360</v>
+      </c>
+      <c r="U31" s="52">
         <f t="shared" si="7"/>
-        <v>1236</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="21"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="53"/>
       <c r="M32" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N32" s="7"/>
-      <c r="O32" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P32" s="47">
+      <c r="O32" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="52">
         <f>((13*2)/10)*P1</f>
         <v>78</v>
       </c>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="47">
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="52">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
-      <c r="T32" s="35">
+      <c r="T32" s="37">
         <f t="shared" si="6"/>
-        <v>2.34</v>
-      </c>
-      <c r="U32" s="47">
+        <v>23.4</v>
+      </c>
+      <c r="U32" s="52">
         <f t="shared" si="7"/>
-        <v>80.34</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="21"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="53"/>
       <c r="M33" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N33" s="7"/>
-      <c r="O33" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="47">
+      <c r="O33" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="52">
         <f>((15*2)/10)*P1</f>
         <v>90</v>
       </c>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="47">
+      <c r="Q33" s="52"/>
+      <c r="R33" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="52">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="37">
         <f t="shared" si="6"/>
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="U33" s="47">
+        <v>27</v>
+      </c>
+      <c r="U33" s="52">
         <f t="shared" si="7"/>
-        <v>92.7</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="21"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="53"/>
       <c r="M34" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N34" s="7"/>
-      <c r="O34" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="47">
+      <c r="O34" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="52">
         <f>((110*2)/10)*P1</f>
         <v>660</v>
       </c>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="47">
+      <c r="Q34" s="52"/>
+      <c r="R34" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="52">
         <f t="shared" si="5"/>
         <v>660</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="37">
         <f t="shared" si="6"/>
-        <v>19.8</v>
-      </c>
-      <c r="U34" s="47">
+        <v>198</v>
+      </c>
+      <c r="U34" s="52">
         <f t="shared" si="7"/>
-        <v>679.8</v>
+        <v>858</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="21"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="53"/>
       <c r="M35" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N35" s="7"/>
-      <c r="O35" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P35" s="47">
+      <c r="O35" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="52">
         <f>((80*2)/10)*P1</f>
         <v>480</v>
       </c>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="47">
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="52">
         <f t="shared" si="5"/>
         <v>480</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="37">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+      <c r="U35" s="52">
+        <f t="shared" si="7"/>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="53"/>
+      <c r="M36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="7"/>
+      <c r="O36" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="52">
+        <f>((9*2)/10)*P1</f>
+        <v>54</v>
+      </c>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="52">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="T36" s="37">
+        <f t="shared" si="6"/>
+        <v>16.2</v>
+      </c>
+      <c r="U36" s="52">
+        <f t="shared" si="7"/>
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="53"/>
+      <c r="M37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="7"/>
+      <c r="O37" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="52">
+        <f>((20*2)/10)*P1</f>
+        <v>120</v>
+      </c>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="52">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="T37" s="37">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+      <c r="U37" s="52">
+        <f t="shared" si="7"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="53"/>
+      <c r="M38" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="7"/>
+      <c r="O38" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="52">
+        <f>((6*2)/10)*P1</f>
+        <v>36</v>
+      </c>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="52">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="T38" s="37">
+        <f t="shared" si="6"/>
+        <v>10.799999999999999</v>
+      </c>
+      <c r="U38" s="52">
+        <f t="shared" si="7"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="53"/>
+      <c r="M39" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="7"/>
+      <c r="O39" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="52">
+        <f>((8*2)/10)*P1</f>
+        <v>48</v>
+      </c>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="52">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="T39" s="37">
         <f t="shared" si="6"/>
         <v>14.399999999999999</v>
       </c>
-      <c r="U35" s="47">
+      <c r="U39" s="52">
         <f t="shared" si="7"/>
-        <v>494.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="21"/>
-      <c r="M36" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N36" s="7"/>
-      <c r="O36" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="47">
-        <f>((9*2)/10)*P1</f>
-        <v>54</v>
-      </c>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="47">
-        <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-      <c r="T36" s="35">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="53"/>
+      <c r="M40" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="7"/>
+      <c r="O40" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="52">
+        <f>((8*2)/10)*P1</f>
+        <v>48</v>
+      </c>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="52">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="T40" s="37">
         <f t="shared" si="6"/>
-        <v>1.6199999999999999</v>
-      </c>
-      <c r="U36" s="47">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U40" s="52">
         <f t="shared" si="7"/>
-        <v>55.62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="49"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="21"/>
-      <c r="M37" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="7"/>
-      <c r="O37" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P37" s="47">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="53"/>
+      <c r="M41" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="53"/>
+      <c r="O41" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="52">
+        <f>((40*2)/10)*P1</f>
+        <v>240</v>
+      </c>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="52">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="T41" s="37">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
+      <c r="U41" s="52">
+        <f t="shared" si="7"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="53"/>
+      <c r="M42" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="53"/>
+      <c r="O42" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="52">
+        <f>((7*2)/10)*P1</f>
+        <v>42</v>
+      </c>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="52">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="T42" s="37">
+        <f t="shared" si="6"/>
+        <v>12.6</v>
+      </c>
+      <c r="U42" s="52">
+        <f t="shared" si="7"/>
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="53"/>
+      <c r="M43" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="53"/>
+      <c r="O43" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="52">
+        <f>((8*2)/10)*P1</f>
+        <v>48</v>
+      </c>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="52">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="T43" s="37">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U43" s="52">
+        <f t="shared" si="7"/>
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="53"/>
+      <c r="M44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="53"/>
+      <c r="O44" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="52">
+        <f>((10*2)/10)*P1</f>
+        <v>60</v>
+      </c>
+      <c r="Q44" s="52"/>
+      <c r="R44" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="52">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="T44" s="37">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="U44" s="52">
+        <f t="shared" si="7"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="53"/>
+      <c r="M45" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N45" s="53"/>
+      <c r="O45" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="52">
+        <f>((6*2)/10)*P1</f>
+        <v>36</v>
+      </c>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="52">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="T45" s="37">
+        <f t="shared" si="6"/>
+        <v>10.799999999999999</v>
+      </c>
+      <c r="U45" s="52">
+        <f t="shared" si="7"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="53"/>
+      <c r="M46" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="53"/>
+      <c r="O46" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="52">
+        <f>((8*2)/10)*P1</f>
+        <v>48</v>
+      </c>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="52">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="T46" s="37">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U46" s="52">
+        <f t="shared" si="7"/>
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="55"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="53"/>
+      <c r="M47" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N47" s="53"/>
+      <c r="O47" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P47" s="52">
         <f>((20*2)/10)*P1</f>
         <v>120</v>
       </c>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="47">
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="52">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="T37" s="35">
+      <c r="T47" s="37">
         <f t="shared" si="6"/>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="U37" s="47">
+        <v>36</v>
+      </c>
+      <c r="U47" s="52">
         <f t="shared" si="7"/>
-        <v>123.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="21"/>
-      <c r="M38" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="7"/>
-      <c r="O38" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="47">
-        <f>((6*2)/10)*P1</f>
-        <v>36</v>
-      </c>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="47">
-        <f t="shared" si="5"/>
-        <v>36</v>
-      </c>
-      <c r="T38" s="35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="55"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="53"/>
+      <c r="M48" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="53"/>
+      <c r="O48" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="52">
+        <f>((36*2)/10)*P1</f>
+        <v>216</v>
+      </c>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="52">
+        <f t="shared" si="5"/>
+        <v>216</v>
+      </c>
+      <c r="T48" s="37">
         <f t="shared" si="6"/>
-        <v>1.08</v>
-      </c>
-      <c r="U38" s="47">
+        <v>64.8</v>
+      </c>
+      <c r="U48" s="52">
         <f t="shared" si="7"/>
-        <v>37.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L39" s="21"/>
-      <c r="M39" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N39" s="7"/>
-      <c r="O39" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P39" s="47">
+        <v>280.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="53"/>
+      <c r="M49" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="53"/>
+      <c r="O49" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="52">
+        <f>((25*2)/10)*P1</f>
+        <v>150</v>
+      </c>
+      <c r="Q49" s="52"/>
+      <c r="R49" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="52">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="T49" s="37">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="U49" s="52">
+        <f t="shared" si="7"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="53"/>
+      <c r="M50" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="53"/>
+      <c r="O50" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="52">
+        <f>((10*2)/10)*P1</f>
+        <v>60</v>
+      </c>
+      <c r="Q50" s="52"/>
+      <c r="R50" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="52">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="T50" s="37">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="U50" s="52">
+        <f t="shared" si="7"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="53"/>
+      <c r="M51" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="53"/>
+      <c r="O51" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="52">
         <f>((8*2)/10)*P1</f>
         <v>48</v>
       </c>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="47">
+      <c r="Q51" s="52"/>
+      <c r="R51" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="52">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="T39" s="35">
+      <c r="T51" s="37">
         <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U39" s="47">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U51" s="52">
         <f t="shared" si="7"/>
-        <v>49.44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="21"/>
-      <c r="M40" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N40" s="7"/>
-      <c r="O40" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P40" s="47">
-        <f>((8*2)/10)*P1</f>
-        <v>48</v>
-      </c>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="47">
-        <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="T40" s="35">
-        <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U40" s="47">
-        <f t="shared" si="7"/>
-        <v>49.44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N41" s="21"/>
-      <c r="O41" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P41" s="47">
-        <f>((40*2)/10)*P1</f>
-        <v>240</v>
-      </c>
-      <c r="Q41" s="47"/>
-      <c r="R41" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="47">
-        <f t="shared" si="5"/>
-        <v>240</v>
-      </c>
-      <c r="T41" s="35">
-        <f t="shared" si="6"/>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="U41" s="47">
-        <f t="shared" si="7"/>
-        <v>247.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="21"/>
-      <c r="M42" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="21"/>
-      <c r="O42" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="47">
-        <f>((7*2)/10)*P1</f>
-        <v>42</v>
-      </c>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="47">
-        <f t="shared" si="5"/>
-        <v>42</v>
-      </c>
-      <c r="T42" s="35">
-        <f t="shared" si="6"/>
-        <v>1.26</v>
-      </c>
-      <c r="U42" s="47">
-        <f t="shared" si="7"/>
-        <v>43.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L43" s="21"/>
-      <c r="M43" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N43" s="21"/>
-      <c r="O43" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="47">
-        <f>((8*2)/10)*P1</f>
-        <v>48</v>
-      </c>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="47">
-        <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="T43" s="35">
-        <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U43" s="47">
-        <f t="shared" si="7"/>
-        <v>49.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L44" s="21"/>
-      <c r="M44" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N44" s="21"/>
-      <c r="O44" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P44" s="47">
-        <f>((10*2)/10)*P1</f>
-        <v>60</v>
-      </c>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="47">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="T44" s="35">
-        <f t="shared" si="6"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="U44" s="47">
-        <f t="shared" si="7"/>
-        <v>61.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L45" s="21"/>
-      <c r="M45" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="21"/>
-      <c r="O45" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="47">
-        <f>((6*2)/10)*P1</f>
-        <v>36</v>
-      </c>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="47">
-        <f t="shared" si="5"/>
-        <v>36</v>
-      </c>
-      <c r="T45" s="35">
-        <f t="shared" si="6"/>
-        <v>1.08</v>
-      </c>
-      <c r="U45" s="47">
-        <f t="shared" si="7"/>
-        <v>37.08</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B46" s="49"/>
-      <c r="C46" s="49"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L46" s="21"/>
-      <c r="M46" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N46" s="21"/>
-      <c r="O46" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P46" s="47">
-        <f>((8*2)/10)*P1</f>
-        <v>48</v>
-      </c>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S46" s="47">
-        <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="T46" s="35">
-        <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U46" s="47">
-        <f t="shared" si="7"/>
-        <v>49.44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L47" s="21"/>
-      <c r="M47" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N47" s="21"/>
-      <c r="O47" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P47" s="47">
-        <f>((20*2)/10)*P1</f>
-        <v>120</v>
-      </c>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S47" s="47">
-        <f t="shared" si="5"/>
-        <v>120</v>
-      </c>
-      <c r="T47" s="35">
-        <f t="shared" si="6"/>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="U47" s="47">
-        <f t="shared" si="7"/>
-        <v>123.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="21"/>
-      <c r="M48" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N48" s="21"/>
-      <c r="O48" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="47">
-        <f>((36*2)/10)*P1</f>
-        <v>216</v>
-      </c>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S48" s="47">
-        <f t="shared" si="5"/>
-        <v>216</v>
-      </c>
-      <c r="T48" s="35">
-        <f t="shared" si="6"/>
-        <v>6.4799999999999995</v>
-      </c>
-      <c r="U48" s="47">
-        <f t="shared" si="7"/>
-        <v>222.48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="21"/>
-      <c r="M49" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="21"/>
-      <c r="O49" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="47">
-        <f>((25*2)/10)*P1</f>
-        <v>150</v>
-      </c>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="47">
-        <f t="shared" si="5"/>
-        <v>150</v>
-      </c>
-      <c r="T49" s="35">
-        <f t="shared" si="6"/>
-        <v>4.5</v>
-      </c>
-      <c r="U49" s="47">
-        <f t="shared" si="7"/>
-        <v>154.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="21"/>
-      <c r="M50" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="21"/>
-      <c r="O50" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="47">
-        <f>((10*2)/10)*P1</f>
-        <v>60</v>
-      </c>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="47">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="T50" s="35">
-        <f t="shared" si="6"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="U50" s="47">
-        <f t="shared" si="7"/>
-        <v>61.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="49"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="21"/>
-      <c r="M51" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N51" s="21"/>
-      <c r="O51" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="47">
-        <f>((8*2)/10)*P1</f>
-        <v>48</v>
-      </c>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="47">
-        <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="T51" s="35">
-        <f t="shared" si="6"/>
-        <v>1.44</v>
-      </c>
-      <c r="U51" s="47">
-        <f t="shared" si="7"/>
-        <v>49.44</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="50"/>
-      <c r="J52" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L52" s="21"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="53"/>
       <c r="M52" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N52" s="21"/>
-      <c r="O52" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P52" s="47">
+      <c r="N52" s="53"/>
+      <c r="O52" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="52">
         <f>((107*2)/10)*P1</f>
         <v>642</v>
       </c>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="47">
+      <c r="Q52" s="52"/>
+      <c r="R52" s="52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="52">
         <f t="shared" si="5"/>
         <v>642</v>
       </c>
-      <c r="T52" s="35">
+      <c r="T52" s="37">
         <f t="shared" si="6"/>
-        <v>19.259999999999998</v>
-      </c>
-      <c r="U52" s="47">
+        <v>192.6</v>
+      </c>
+      <c r="U52" s="52">
         <f t="shared" si="7"/>
-        <v>661.26</v>
+        <v>834.6</v>
       </c>
     </row>
   </sheetData>
@@ -9603,15 +9619,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C1" s="46">
+      <c r="C1" s="51">
         <v>30</v>
       </c>
-      <c r="D1" s="54">
+      <c r="D1" s="61">
         <v>87</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="55">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="62">
         <v>52.67</v>
       </c>
     </row>
@@ -9643,7 +9659,7 @@
       <c r="I2" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="38" t="s">
         <v>48</v>
       </c>
     </row>
@@ -9654,7 +9670,7 @@
       <c r="B3" s="31">
         <v>5</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -9671,7 +9687,7 @@
         <f>B3*$G$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="37">
         <f>E3+F3+G3</f>
         <v>1298.3499999999999</v>
       </c>
@@ -9691,7 +9707,7 @@
       <c r="B4" s="26">
         <v>5</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -9708,7 +9724,7 @@
         <f t="shared" ref="G4:G51" si="2">B4*$G$1</f>
         <v>263.35000000000002</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="37">
         <f t="shared" ref="H4:H52" si="3">E4+F4+G4</f>
         <v>1298.3499999999999</v>
       </c>
@@ -9728,7 +9744,7 @@
       <c r="B5" s="24">
         <v>5</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="52">
         <f>((100*2)/10)*C1</f>
         <v>600</v>
       </c>
@@ -9745,7 +9761,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="37">
         <f t="shared" si="3"/>
         <v>1298.3499999999999</v>
       </c>
@@ -9765,7 +9781,7 @@
       <c r="B6" s="26">
         <v>2</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -9782,7 +9798,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -9802,7 +9818,7 @@
       <c r="B7" s="24">
         <v>3</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -9819,7 +9835,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -9839,7 +9855,7 @@
       <c r="B8" s="26">
         <v>3</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="52">
         <f>((40*2)/10)*C1</f>
         <v>240</v>
       </c>
@@ -9856,7 +9872,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="37">
         <f t="shared" si="3"/>
         <v>659.01</v>
       </c>
@@ -9876,7 +9892,7 @@
       <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -9893,7 +9909,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -9913,7 +9929,7 @@
       <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="52">
         <f>((16*2)/10)*C8</f>
         <v>768</v>
       </c>
@@ -9930,7 +9946,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="37">
         <f t="shared" si="3"/>
         <v>1047.3399999999999</v>
       </c>
@@ -9950,7 +9966,7 @@
       <c r="B11" s="24">
         <v>5</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -9967,7 +9983,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -9987,7 +10003,7 @@
       <c r="B12" s="26">
         <v>5</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -10004,7 +10020,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -10024,7 +10040,7 @@
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="52">
         <f>((45*2)/10)*C1</f>
         <v>270</v>
       </c>
@@ -10041,7 +10057,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="37">
         <f t="shared" si="3"/>
         <v>689.01</v>
       </c>
@@ -10061,7 +10077,7 @@
       <c r="B14" s="26">
         <v>3</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="52">
         <f>((11*2)/10)*C1</f>
         <v>66</v>
       </c>
@@ -10078,7 +10094,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="37">
         <f t="shared" si="3"/>
         <v>485.01</v>
       </c>
@@ -10098,7 +10114,7 @@
       <c r="B15" s="24">
         <v>5</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -10115,7 +10131,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -10135,7 +10151,7 @@
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="52">
         <f>((35*2)/10)*C1</f>
         <v>210</v>
       </c>
@@ -10152,7 +10168,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="37">
         <f t="shared" si="3"/>
         <v>629.01</v>
       </c>
@@ -10172,7 +10188,7 @@
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="52">
         <f>((35*2)/10)*C1</f>
         <v>210</v>
       </c>
@@ -10189,7 +10205,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>629.01</v>
       </c>
@@ -10209,7 +10225,7 @@
       <c r="B18" s="26">
         <v>3</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="52">
         <f>((37*2)/10)*C1</f>
         <v>222</v>
       </c>
@@ -10226,7 +10242,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="37">
         <f t="shared" si="3"/>
         <v>641.01</v>
       </c>
@@ -10246,7 +10262,7 @@
       <c r="B19" s="24">
         <v>2</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="52">
         <f>((9*2)/10)*C1</f>
         <v>54</v>
       </c>
@@ -10263,7 +10279,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="37">
         <f t="shared" si="3"/>
         <v>333.34000000000003</v>
       </c>
@@ -10283,7 +10299,7 @@
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -10300,7 +10316,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -10320,7 +10336,7 @@
       <c r="B21" s="24">
         <v>2</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -10337,7 +10353,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -10357,7 +10373,7 @@
       <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -10374,7 +10390,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -10394,7 +10410,7 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="52">
         <f>((27*2)/10)*C1</f>
         <v>162</v>
       </c>
@@ -10411,7 +10427,7 @@
         <f t="shared" si="2"/>
         <v>52.67</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="37">
         <f t="shared" si="3"/>
         <v>301.67</v>
       </c>
@@ -10431,7 +10447,7 @@
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="52">
         <f>((76*2)/10)*C1</f>
         <v>456</v>
       </c>
@@ -10448,7 +10464,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="37">
         <f t="shared" si="3"/>
         <v>875.01</v>
       </c>
@@ -10468,7 +10484,7 @@
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -10485,7 +10501,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -10505,7 +10521,7 @@
       <c r="B26" s="26">
         <v>3</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="52">
         <f>((70*2)/10)*C1</f>
         <v>420</v>
       </c>
@@ -10522,7 +10538,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="37">
         <f t="shared" si="3"/>
         <v>839.01</v>
       </c>
@@ -10542,7 +10558,7 @@
       <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -10559,7 +10575,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -10579,7 +10595,7 @@
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="52">
         <f>((16*2)/10)*C1</f>
         <v>96</v>
       </c>
@@ -10596,7 +10612,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="37">
         <f t="shared" si="3"/>
         <v>515.01</v>
       </c>
@@ -10616,7 +10632,7 @@
       <c r="B29" s="24">
         <v>2</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="52">
         <f>((32*2)/10)*C1</f>
         <v>192</v>
       </c>
@@ -10633,7 +10649,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="37">
         <f t="shared" si="3"/>
         <v>471.34000000000003</v>
       </c>
@@ -10653,7 +10669,7 @@
       <c r="B30" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -10670,7 +10686,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -10690,7 +10706,7 @@
       <c r="B31" s="24">
         <v>5</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="52">
         <f>((200*2)/10)*C1</f>
         <v>1200</v>
       </c>
@@ -10707,7 +10723,7 @@
         <f t="shared" si="2"/>
         <v>263.35000000000002</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="37">
         <f t="shared" si="3"/>
         <v>1898.35</v>
       </c>
@@ -10727,7 +10743,7 @@
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="52">
         <f>((13*2)/10)*C1</f>
         <v>78</v>
       </c>
@@ -10744,7 +10760,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="37">
         <f t="shared" si="3"/>
         <v>357.34000000000003</v>
       </c>
@@ -10764,7 +10780,7 @@
       <c r="B33" s="24">
         <v>2</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="52">
         <f>((15*2)/10)*C1</f>
         <v>90</v>
       </c>
@@ -10781,7 +10797,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="37">
         <f t="shared" si="3"/>
         <v>369.34000000000003</v>
       </c>
@@ -10795,13 +10811,13 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="39" t="s">
         <v>51</v>
       </c>
       <c r="B34" s="26">
         <v>4</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="52">
         <f>((110*2)/10)*C1</f>
         <v>660</v>
       </c>
@@ -10818,7 +10834,7 @@
         <f t="shared" si="2"/>
         <v>210.68</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="37">
         <f t="shared" si="3"/>
         <v>1218.68</v>
       </c>
@@ -10832,13 +10848,13 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="40">
         <v>4</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="52">
         <f>((80*2)/10)*C1</f>
         <v>480</v>
       </c>
@@ -10855,7 +10871,7 @@
         <f t="shared" si="2"/>
         <v>210.68</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="37">
         <f t="shared" si="3"/>
         <v>1038.68</v>
       </c>
@@ -10869,13 +10885,13 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="39" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="24">
         <v>3</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="52">
         <f>((9*2)/10)*C1</f>
         <v>54</v>
       </c>
@@ -10892,7 +10908,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="37">
         <f t="shared" si="3"/>
         <v>473.01</v>
       </c>
@@ -10906,13 +10922,13 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="24">
         <v>3</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="52">
         <f>((20*2)/10)*C1</f>
         <v>120</v>
       </c>
@@ -10929,7 +10945,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H37" s="35">
+      <c r="H37" s="37">
         <f t="shared" si="3"/>
         <v>539.01</v>
       </c>
@@ -10943,13 +10959,13 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="39" t="s">
         <v>55</v>
       </c>
       <c r="B38" s="24">
         <v>2</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -10966,7 +10982,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -10980,13 +10996,13 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="24">
         <v>2</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -11003,7 +11019,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -11017,13 +11033,13 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="39" t="s">
         <v>58</v>
       </c>
       <c r="B40" s="24">
         <v>2</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -11040,7 +11056,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H40" s="35">
+      <c r="H40" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -11054,13 +11070,13 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="24">
         <v>2</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="52">
         <f>((40*2)/10)*C1</f>
         <v>240</v>
       </c>
@@ -11077,7 +11093,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="37">
         <f t="shared" si="3"/>
         <v>519.34</v>
       </c>
@@ -11091,13 +11107,13 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="39" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="26">
         <v>3</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="52">
         <f>((7*2)/10)*C1</f>
         <v>42</v>
       </c>
@@ -11114,7 +11130,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="37">
         <f t="shared" si="3"/>
         <v>461.01</v>
       </c>
@@ -11128,13 +11144,13 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="39" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="24">
         <v>2</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -11151,7 +11167,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H43" s="35">
+      <c r="H43" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -11165,13 +11181,13 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="39" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="24">
         <v>2</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -11188,7 +11204,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -11202,13 +11218,13 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="39" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="24">
         <v>2</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="52">
         <f>((6*2)/10)*C1</f>
         <v>36</v>
       </c>
@@ -11225,7 +11241,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="37">
         <f t="shared" si="3"/>
         <v>315.34000000000003</v>
       </c>
@@ -11239,13 +11255,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="39" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="24">
         <v>2</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="52">
         <f>((8*2)/10)*C1</f>
         <v>48</v>
       </c>
@@ -11262,7 +11278,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="37">
         <f t="shared" si="3"/>
         <v>327.34000000000003</v>
       </c>
@@ -11276,13 +11292,13 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="39" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="24">
         <v>2</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="52">
         <f>((20*2)/10)*C1</f>
         <v>120</v>
       </c>
@@ -11299,7 +11315,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="37">
         <f t="shared" si="3"/>
         <v>399.34000000000003</v>
       </c>
@@ -11313,13 +11329,13 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="39" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="24">
         <v>2</v>
       </c>
-      <c r="C48" s="47">
+      <c r="C48" s="52">
         <f>((36*2)/10)*C1</f>
         <v>216</v>
       </c>
@@ -11336,7 +11352,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="37">
         <f t="shared" si="3"/>
         <v>495.34000000000003</v>
       </c>
@@ -11350,13 +11366,13 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="39" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="26">
         <v>3</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="52">
         <f>((25*2)/10)*C1</f>
         <v>150</v>
       </c>
@@ -11373,7 +11389,7 @@
         <f t="shared" si="2"/>
         <v>158.01</v>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="37">
         <f t="shared" si="3"/>
         <v>569.01</v>
       </c>
@@ -11387,13 +11403,13 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="39" t="s">
         <v>69</v>
       </c>
       <c r="B50" s="26">
         <v>2</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="52">
         <f>((10*2)/10)*C1</f>
         <v>60</v>
       </c>
@@ -11410,7 +11426,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -11424,13 +11440,13 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="39" t="s">
         <v>70</v>
       </c>
       <c r="B51" s="24">
         <v>2</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="52">
         <f>((10*2)/10)*$C$1</f>
         <v>60</v>
       </c>
@@ -11447,7 +11463,7 @@
         <f t="shared" si="2"/>
         <v>105.34</v>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="37">
         <f t="shared" si="3"/>
         <v>339.34000000000003</v>
       </c>
@@ -11461,13 +11477,13 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="39" t="s">
         <v>85</v>
       </c>
       <c r="B52" s="24">
         <v>4</v>
       </c>
-      <c r="C52" s="47">
+      <c r="C52" s="52">
         <f>((8*2)/10)*$C$1</f>
         <v>48</v>
       </c>
@@ -11479,12 +11495,12 @@
         <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="F52" s="21"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="18">
         <f>B52*$G$1</f>
         <v>210.68</v>
       </c>
-      <c r="H52" s="35">
+      <c r="H52" s="37">
         <f t="shared" si="3"/>
         <v>606.68000000000006</v>
       </c>
@@ -11498,8 +11514,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="38"/>
-      <c r="G53" s="53"/>
+      <c r="A53" s="43"/>
+      <c r="G53" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
